--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,178 +656,191 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F8" s="3">
         <v>15300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>14100</v>
       </c>
-      <c r="F8" s="3">
-        <v>13000</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>13200</v>
+      </c>
+      <c r="I8" s="3">
         <v>12700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>11900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>22600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>11200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>11100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>11500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>22300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>11700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>9500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>9400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>9200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>9700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>9600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>8900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>8400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -894,8 +907,14 @@
       <c r="X9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -962,8 +981,14 @@
       <c r="X10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1013,10 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1083,14 @@
       <c r="X12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1157,14 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1192,19 +1231,25 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
         <v>-100</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>5</v>
+      <c r="E15" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="3">
+        <v>-100</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>5</v>
@@ -1218,11 +1263,11 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1260,8 +1305,14 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1334,158 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F17" s="3">
         <v>5500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4000</v>
       </c>
-      <c r="F17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1900</v>
-      </c>
-      <c r="R17" s="3">
-        <v>2200</v>
       </c>
       <c r="S17" s="3">
         <v>1900</v>
       </c>
       <c r="T17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V17" s="3">
         <v>2300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>11400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F18" s="3">
         <v>9800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>10100</v>
       </c>
-      <c r="F18" s="3">
-        <v>10300</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="I18" s="3">
         <v>11400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>20900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>10200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>11300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>20100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>9200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>7700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>7500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>7000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>7600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>7400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>7200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>6800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-3000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,76 +1510,84 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="F20" s="3">
         <v>-6800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-6300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-5900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-11100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-5200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-8600</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-7400</v>
       </c>
       <c r="M20" s="3">
         <v>-8600</v>
       </c>
       <c r="N20" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="P20" s="3">
         <v>-4300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-5700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-3800</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-5200</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-3100</v>
       </c>
       <c r="S20" s="3">
         <v>-5200</v>
       </c>
       <c r="T20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="V20" s="3">
         <v>-3700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-3500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-3400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>6600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1581,8 +1654,14 @@
       <c r="X21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1644,57 +1723,63 @@
         <v>0</v>
       </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F23" s="3">
         <v>3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>4400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>3400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>7200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>9800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>5000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>3900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>11500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3600</v>
-      </c>
-      <c r="P23" s="3">
-        <v>4000</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>2300</v>
       </c>
       <c r="R23" s="3">
         <v>4000</v>
@@ -1703,22 +1788,28 @@
         <v>2300</v>
       </c>
       <c r="T23" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U23" s="3">
+        <v>2300</v>
+      </c>
+      <c r="V23" s="3">
         <v>3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>3400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>2000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1726,67 +1817,73 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
-      </c>
-      <c r="P24" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>600</v>
       </c>
       <c r="S24" s="3">
+        <v>300</v>
+      </c>
+      <c r="T24" s="3">
+        <v>600</v>
+      </c>
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1950,162 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>900</v>
+      </c>
+      <c r="F26" s="3">
         <v>2500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>3300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>8300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>2000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2900</v>
-      </c>
-      <c r="P26" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>2100</v>
       </c>
       <c r="R26" s="3">
         <v>3400</v>
       </c>
       <c r="S26" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T26" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U26" s="3">
         <v>1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>3200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>3300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>900</v>
+      </c>
+      <c r="F27" s="3">
         <v>2500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>3300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>8300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>4300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>9200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>5300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
-      </c>
-      <c r="P27" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>2100</v>
       </c>
       <c r="R27" s="3">
         <v>3400</v>
       </c>
       <c r="S27" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U27" s="3">
         <v>1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>3200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>3300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2172,14 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2246,14 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2320,14 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2394,162 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E32" s="3">
+        <v>9500</v>
+      </c>
+      <c r="F32" s="3">
         <v>6800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>6300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>5900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>11100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>5200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>8600</v>
-      </c>
-      <c r="L32" s="3">
-        <v>7400</v>
       </c>
       <c r="M32" s="3">
         <v>8600</v>
       </c>
       <c r="N32" s="3">
+        <v>7400</v>
+      </c>
+      <c r="O32" s="3">
+        <v>8600</v>
+      </c>
+      <c r="P32" s="3">
         <v>4300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>5700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>3800</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>5200</v>
-      </c>
-      <c r="R32" s="3">
-        <v>3100</v>
       </c>
       <c r="S32" s="3">
         <v>5200</v>
       </c>
       <c r="T32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>5200</v>
+      </c>
+      <c r="V32" s="3">
         <v>3700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>3500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>3400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-6600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>900</v>
+      </c>
+      <c r="F33" s="3">
         <v>2500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>3300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>8300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>9200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>5300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
-      </c>
-      <c r="P33" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>2100</v>
       </c>
       <c r="R33" s="3">
         <v>3400</v>
       </c>
       <c r="S33" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T33" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U33" s="3">
         <v>1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>3200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>3300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2616,167 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>900</v>
+      </c>
+      <c r="F35" s="3">
         <v>2500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>3300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>8300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>9200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>5300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
-      </c>
-      <c r="P35" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>2100</v>
       </c>
       <c r="R35" s="3">
         <v>3400</v>
       </c>
       <c r="S35" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T35" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U35" s="3">
         <v>1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>3200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>3300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2801,10 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,144 +2829,158 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>67400</v>
+      </c>
+      <c r="F41" s="3">
         <v>58000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>58400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>59800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>52100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>50600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>58600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>54000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>45000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>43400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>50000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>39800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>31200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>39900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>47000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>50100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>42400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>68500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>49400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>50500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>81400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F42" s="3">
         <v>3900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>9900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>4700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>4800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>4900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>6700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>6700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>7700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>7500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>23300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>28500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>59500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>46100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>16000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>6700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>35700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>2000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>35400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>37400</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2862,8 +3047,14 @@
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2930,8 +3121,14 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2998,8 +3195,14 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3066,8 +3269,14 @@
       <c r="X46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3129,93 +3338,105 @@
         <v>0</v>
       </c>
       <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>730900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F48" s="3">
         <v>22400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>22700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>23200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>23900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>23700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>23700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>22900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>22800</v>
       </c>
       <c r="L48" s="3">
         <v>22900</v>
       </c>
       <c r="M48" s="3">
+        <v>22800</v>
+      </c>
+      <c r="N48" s="3">
+        <v>22900</v>
+      </c>
+      <c r="O48" s="3">
         <v>22600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>22000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>20800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>20600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>20600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>18500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>18300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>18200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>18100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>17600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>16700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F49" s="3">
         <v>7400</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3228,11 +3449,11 @@
       <c r="J49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -3270,8 +3491,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3565,14 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3639,14 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3474,8 +3713,14 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3787,88 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1511900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1471000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1382300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1354800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1331400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1329000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1333900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1342000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1346100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1385800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1328800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1292700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1238300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1204700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1172200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1114700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>951400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>958300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>943700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>934100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>893400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>854800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3893,10 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,25 +3921,27 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>400</v>
-      </c>
-      <c r="G57" s="3">
-        <v>100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>200</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -3692,13 +3953,13 @@
         <v>100</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
+        <v>100</v>
+      </c>
+      <c r="N57" s="3">
         <v>300</v>
-      </c>
-      <c r="M57" s="3">
-        <v>200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>200</v>
       </c>
       <c r="O57" s="3">
         <v>200</v>
@@ -3710,28 +3971,34 @@
         <v>200</v>
       </c>
       <c r="R57" s="3">
+        <v>200</v>
+      </c>
+      <c r="S57" s="3">
+        <v>200</v>
+      </c>
+      <c r="T57" s="3">
         <v>300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>500</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
-      </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3793,13 +4060,19 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>749200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3861,13 +4134,19 @@
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3934,8 +4213,14 @@
       <c r="X60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3970,10 +4255,10 @@
         <v>20000</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -4002,8 +4287,14 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4361,14 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4435,14 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4509,14 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4583,88 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1409300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1372500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1296700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1263900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1242100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1249900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1261800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1256800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1245100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1259700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1200700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1163100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1116300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1082100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1055300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1001500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>846500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>852900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>837600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>832200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>795600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>762000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4689,10 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4759,14 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4833,14 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4907,14 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4981,88 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>100600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>98600</v>
+      </c>
+      <c r="F72" s="3">
         <v>98400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>96600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>94300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>91700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>89100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>83800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>80400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>76800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>75500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>72300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>69000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>64400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>62000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>59200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>57800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>55000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>53700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>6900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>5000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>68300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +5129,14 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5203,14 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5277,88 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>98500</v>
+      </c>
+      <c r="F76" s="3">
         <v>85600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>90900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>89300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>79100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>72200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>85200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>101000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>126100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>128000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>129700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>122000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>122700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>116900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>113200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>104900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>105400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>106100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>101900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>97800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>92700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5425,167 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>900</v>
+      </c>
+      <c r="F81" s="3">
         <v>2500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>3300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>8300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>9200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>5300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
-      </c>
-      <c r="P81" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>2100</v>
       </c>
       <c r="R81" s="3">
         <v>3400</v>
       </c>
       <c r="S81" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T81" s="3">
+        <v>3400</v>
+      </c>
+      <c r="U81" s="3">
         <v>1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>3200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>3300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5610,10 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5283,8 +5680,14 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5754,14 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5828,14 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5902,14 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5976,14 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,8 +6050,14 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5691,8 +6124,14 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +6156,10 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5785,8 +6226,14 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6300,14 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6374,14 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5989,8 +6448,14 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6480,10 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6550,14 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6624,14 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6698,14 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,8 +6772,14 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6355,8 +6846,14 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,8 +6920,14 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6489,6 +6992,12 @@
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,191 +656,198 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E8" s="3">
         <v>18000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15300</v>
       </c>
-      <c r="G8" s="3">
-        <v>14100</v>
-      </c>
       <c r="H8" s="3">
+        <v>14200</v>
+      </c>
+      <c r="I8" s="3">
         <v>13200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -913,8 +920,11 @@
       <c r="Z9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -987,8 +997,11 @@
       <c r="Z10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1180,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1237,8 +1257,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1251,11 +1274,11 @@
       <c r="F15" s="3">
         <v>-100</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
+      <c r="G15" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>5</v>
@@ -1269,8 +1292,8 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1311,8 +1334,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5500</v>
       </c>
-      <c r="G17" s="3">
-        <v>4000</v>
-      </c>
       <c r="H17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I17" s="3">
         <v>2800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>11400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>10500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9800</v>
       </c>
-      <c r="G18" s="3">
-        <v>10100</v>
-      </c>
       <c r="H18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="I18" s="3">
         <v>10400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>9200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,82 +1545,86 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-7200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-6300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-7400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1660,8 +1697,11 @@
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1729,161 +1769,170 @@
         <v>0</v>
       </c>
       <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3">
         <v>1700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2300</v>
-      </c>
-      <c r="V23" s="3">
-        <v>3800</v>
       </c>
       <c r="W23" s="3">
         <v>3800</v>
       </c>
       <c r="X23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y23" s="3">
         <v>3400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>700</v>
       </c>
       <c r="H24" s="3">
         <v>700</v>
       </c>
       <c r="I24" s="3">
+        <v>700</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>600</v>
       </c>
       <c r="R24" s="3">
         <v>600</v>
       </c>
       <c r="S24" s="3">
+        <v>600</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
-      </c>
-      <c r="V24" s="3">
-        <v>500</v>
       </c>
       <c r="W24" s="3">
         <v>500</v>
       </c>
       <c r="X24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Y24" s="3">
         <v>400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E32" s="3">
         <v>7200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>6300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>7400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,156 +2917,163 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71100</v>
+      </c>
+      <c r="E41" s="3">
         <v>66900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>67400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>50600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>58600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>54000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>45000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>43400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>50000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>39800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>47000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>50100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>68500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>50500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>81400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4900</v>
-      </c>
-      <c r="K42" s="3">
-        <v>6700</v>
       </c>
       <c r="L42" s="3">
         <v>6700</v>
       </c>
       <c r="M42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N42" s="3">
         <v>7700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>23300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>28500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>46100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>35700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>2000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>35400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>37400</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
-      </c>
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3053,8 +3146,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,8 +3223,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3201,8 +3300,11 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3275,8 +3377,11 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3344,87 +3449,93 @@
         <v>0</v>
       </c>
       <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="3">
         <v>730900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E48" s="3">
         <v>21600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>22000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>22400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>22700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>23700</v>
       </c>
       <c r="K48" s="3">
         <v>23700</v>
       </c>
       <c r="L48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="M48" s="3">
         <v>22900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>20800</v>
-      </c>
-      <c r="R48" s="3">
-        <v>20600</v>
       </c>
       <c r="S48" s="3">
         <v>20600</v>
       </c>
       <c r="T48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="U48" s="3">
         <v>18500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>17600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>16700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3435,11 +3546,11 @@
         <v>5300</v>
       </c>
       <c r="F49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="G49" s="3">
         <v>7400</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3455,8 +3566,8 @@
       <c r="L49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="M49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3497,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,8 +3762,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3719,8 +3839,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1533100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1511900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1471000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1382300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1354800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1331400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1329000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1333900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1342000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1346100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1385800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1328800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1292700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1238300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1204700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1172200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1114700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>951400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>958300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>943700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>934100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>893400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>854800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,46 +4053,47 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>400</v>
       </c>
       <c r="H57" s="3">
         <v>400</v>
       </c>
       <c r="I57" s="3">
+        <v>400</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
-      </c>
-      <c r="O57" s="3">
-        <v>200</v>
       </c>
       <c r="P57" s="3">
         <v>200</v>
@@ -3977,28 +4108,31 @@
         <v>200</v>
       </c>
       <c r="T57" s="3">
+        <v>200</v>
+      </c>
+      <c r="U57" s="3">
         <v>300</v>
-      </c>
-      <c r="U57" s="3">
-        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>400</v>
       </c>
       <c r="W57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>500</v>
       </c>
       <c r="Y57" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4066,13 +4200,16 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>749200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4140,13 +4277,16 @@
         <v>0</v>
       </c>
       <c r="Y59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -4219,8 +4359,11 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4261,7 +4404,7 @@
         <v>20000</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -4293,8 +4436,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4367,8 +4513,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1427700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1409300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1372500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1296700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1263900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1242100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1249900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1261800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1256800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1245100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1259700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1200700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1163100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1116300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1082100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1055300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1001500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>846500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>852900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>837600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>832200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>795600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>762000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>102900</v>
+      </c>
+      <c r="E72" s="3">
         <v>100600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>98600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>98400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>96600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>94300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>91700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>89100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>83800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>80400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>76800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>75500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>72300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>69000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>64400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>62000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>59200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>57800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>55000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>53700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>68300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>105400</v>
+      </c>
+      <c r="E76" s="3">
         <v>102600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>98500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>85600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>90900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>89300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>79100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>72200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>85200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>101000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>126100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>128000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>129700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>122000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>122700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>116900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>113200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>104900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>105400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>106100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>101900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>97800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>92700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5686,8 +5885,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,8 +6270,11 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6130,8 +6347,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,8 +6378,9 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6232,8 +6453,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,8 +6607,11 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6454,8 +6684,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6556,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,8 +7021,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6852,8 +7098,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6926,8 +7175,11 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6998,6 +7250,9 @@
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,55 +656,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
-      </c>
-      <c r="F7" s="2">
-        <v>45291</v>
       </c>
       <c r="G7" s="2">
         <v>45199</v>
@@ -719,135 +720,141 @@
         <v>44926</v>
       </c>
       <c r="K7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19200</v>
+        <v>18000</v>
       </c>
       <c r="E8" s="3">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="F8" s="3">
-        <v>17100</v>
+        <v>15600</v>
       </c>
       <c r="G8" s="3">
-        <v>15300</v>
+        <v>16200</v>
       </c>
       <c r="H8" s="3">
-        <v>14200</v>
+        <v>16100</v>
       </c>
       <c r="I8" s="3">
-        <v>13200</v>
+        <v>15400</v>
       </c>
       <c r="J8" s="3">
+        <v>15800</v>
+      </c>
+      <c r="K8" s="3">
         <v>12700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>11900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>22300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -923,31 +930,34 @@
       <c r="AA9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>17000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>15600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>16200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>15400</v>
+      </c>
+      <c r="J10" s="3">
+        <v>15800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1000,8 +1010,11 @@
       <c r="AA10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,31 +1200,34 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1260,31 +1280,34 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-100</v>
+        <v>600</v>
       </c>
       <c r="E15" s="3">
-        <v>-100</v>
+        <v>600</v>
       </c>
       <c r="F15" s="3">
-        <v>-100</v>
+        <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>-100</v>
+        <v>500</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+        <v>500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>500</v>
+      </c>
+      <c r="J15" s="3">
+        <v>500</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1295,8 +1318,8 @@
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1337,8 +1360,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>7900</v>
+        <v>14400</v>
       </c>
       <c r="E17" s="3">
-        <v>7500</v>
+        <v>13100</v>
       </c>
       <c r="F17" s="3">
-        <v>6500</v>
+        <v>12100</v>
       </c>
       <c r="G17" s="3">
-        <v>5500</v>
+        <v>13000</v>
       </c>
       <c r="H17" s="3">
-        <v>4200</v>
+        <v>12400</v>
       </c>
       <c r="I17" s="3">
-        <v>2800</v>
+        <v>11000</v>
       </c>
       <c r="J17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>11400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>11400</v>
+      </c>
+      <c r="L18" s="3">
+        <v>11200</v>
+      </c>
+      <c r="M18" s="3">
+        <v>20900</v>
+      </c>
+      <c r="N18" s="3">
+        <v>10200</v>
+      </c>
+      <c r="O18" s="3">
+        <v>10600</v>
+      </c>
+      <c r="P18" s="3">
         <v>11300</v>
       </c>
-      <c r="E18" s="3">
-        <v>10500</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="Q18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="R18" s="3">
         <v>10600</v>
       </c>
-      <c r="G18" s="3">
-        <v>9800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I18" s="3">
-        <v>10400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>11400</v>
-      </c>
-      <c r="K18" s="3">
-        <v>11200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>20900</v>
-      </c>
-      <c r="M18" s="3">
-        <v>10200</v>
-      </c>
-      <c r="N18" s="3">
-        <v>10600</v>
-      </c>
-      <c r="O18" s="3">
-        <v>11300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>20100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>10600</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>9200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,108 +1579,112 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-7600</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>-7200</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>-9500</v>
+        <v>200</v>
       </c>
       <c r="G20" s="3">
-        <v>-6800</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-5900</v>
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>6600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
+      <c r="D21" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="J21" s="3">
+        <v>3900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1700,31 +1737,34 @@
       <c r="AA21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1772,24 +1812,27 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E23" s="3">
         <v>3700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1200</v>
       </c>
       <c r="G23" s="3">
         <v>3000</v>
@@ -1804,69 +1847,72 @@
         <v>3400</v>
       </c>
       <c r="K23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L23" s="3">
         <v>7200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2300</v>
-      </c>
-      <c r="W23" s="3">
-        <v>3800</v>
       </c>
       <c r="X23" s="3">
         <v>3800</v>
       </c>
       <c r="Y23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z23" s="3">
         <v>3400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>300</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
@@ -1881,58 +1927,61 @@
         <v>100</v>
       </c>
       <c r="K24" s="3">
+        <v>100</v>
+      </c>
+      <c r="L24" s="3">
         <v>1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1000</v>
-      </c>
-      <c r="R24" s="3">
-        <v>600</v>
       </c>
       <c r="S24" s="3">
         <v>600</v>
       </c>
       <c r="T24" s="3">
+        <v>600</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
-      </c>
-      <c r="W24" s="3">
-        <v>500</v>
       </c>
       <c r="X24" s="3">
         <v>500</v>
       </c>
       <c r="Y24" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,19 +2057,22 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2700</v>
-      </c>
-      <c r="F26" s="3">
-        <v>900</v>
       </c>
       <c r="G26" s="3">
         <v>2500</v>
@@ -2035,69 +2087,72 @@
         <v>3300</v>
       </c>
       <c r="K26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L26" s="3">
         <v>5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2700</v>
-      </c>
-      <c r="F27" s="3">
-        <v>900</v>
       </c>
       <c r="G27" s="3">
         <v>2500</v>
@@ -2112,58 +2167,61 @@
         <v>3300</v>
       </c>
       <c r="K27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L27" s="3">
         <v>5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,96 +2537,102 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>7600</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>7200</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>9500</v>
+        <v>-200</v>
       </c>
       <c r="G32" s="3">
-        <v>6800</v>
+        <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>6300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>5900</v>
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2700</v>
-      </c>
-      <c r="F33" s="3">
-        <v>900</v>
       </c>
       <c r="G33" s="3">
         <v>2500</v>
@@ -2574,58 +2647,61 @@
         <v>3300</v>
       </c>
       <c r="K33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L33" s="3">
         <v>5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,19 +2777,22 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2700</v>
-      </c>
-      <c r="F35" s="3">
-        <v>900</v>
       </c>
       <c r="G35" s="3">
         <v>2500</v>
@@ -2728,74 +2807,77 @@
         <v>3300</v>
       </c>
       <c r="K35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L35" s="3">
         <v>5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
-      </c>
-      <c r="F38" s="2">
-        <v>45291</v>
       </c>
       <c r="G38" s="2">
         <v>45199</v>
@@ -2810,58 +2892,61 @@
         <v>44926</v>
       </c>
       <c r="K38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,185 +3004,192 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>71100</v>
+        <v>37200</v>
       </c>
       <c r="E41" s="3">
-        <v>66900</v>
+        <v>39200</v>
       </c>
       <c r="F41" s="3">
-        <v>67400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>58000</v>
+        <v>29100</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="3">
-        <v>58400</v>
+        <v>26400</v>
       </c>
       <c r="I41" s="3">
-        <v>59800</v>
+        <v>25200</v>
       </c>
       <c r="J41" s="3">
+        <v>26400</v>
+      </c>
+      <c r="K41" s="3">
         <v>52100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>50600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>54000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>45000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>43400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>50000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>39800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>31200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>47000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>50100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>42400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>68500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>49400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>50500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>81400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>6100</v>
+        <v>34800</v>
       </c>
       <c r="E42" s="3">
-        <v>5000</v>
+        <v>9300</v>
       </c>
       <c r="F42" s="3">
-        <v>5600</v>
+        <v>11200</v>
       </c>
       <c r="G42" s="3">
-        <v>3900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>9900</v>
+        <v>15400</v>
       </c>
       <c r="I42" s="3">
-        <v>4700</v>
+        <v>9400</v>
       </c>
       <c r="J42" s="3">
+        <v>8100</v>
+      </c>
+      <c r="K42" s="3">
         <v>4800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4900</v>
-      </c>
-      <c r="L42" s="3">
-        <v>6700</v>
       </c>
       <c r="M42" s="3">
         <v>6700</v>
       </c>
       <c r="N42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O42" s="3">
         <v>7700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>23300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>28500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>59500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>46100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>16000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>35700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>2000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>35400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>37400</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3149,31 +3242,34 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E44" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
+        <v>800</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H44" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I44" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3226,31 +3322,34 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>36700</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>38900</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
+        <v>44200</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>37400</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>40200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>33100</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3303,31 +3402,34 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>110000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>88500</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
+        <v>85400</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>80600</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>75800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>68600</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -3380,31 +3482,34 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>521400</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>495300</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+        <v>500700</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>421000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>434900</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>449700</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3452,27 +3557,30 @@
         <v>0</v>
       </c>
       <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3">
         <v>730900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E48" s="3">
         <v>21200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21600</v>
       </c>
-      <c r="F48" s="3">
-        <v>22000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>22400</v>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
         <v>22700</v>
@@ -3484,58 +3592,61 @@
         <v>23900</v>
       </c>
       <c r="K48" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="L48" s="3">
         <v>23700</v>
       </c>
       <c r="M48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="N48" s="3">
         <v>22900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>20800</v>
-      </c>
-      <c r="S48" s="3">
-        <v>20600</v>
       </c>
       <c r="T48" s="3">
         <v>20600</v>
       </c>
       <c r="U48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="V48" s="3">
         <v>18500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>16700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3549,16 +3660,16 @@
         <v>5300</v>
       </c>
       <c r="G49" s="3">
-        <v>7400</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -3569,8 +3680,8 @@
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,31 +3882,34 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>68500</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>55900</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
+        <v>55100</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>62400</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>52600</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>38400</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3842,8 +3962,11 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,22 +4042,25 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1589300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1533100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1511900</v>
       </c>
-      <c r="F54" s="3">
-        <v>1471000</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1382300</v>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H54" s="3">
         <v>1354800</v>
@@ -3946,58 +4072,61 @@
         <v>1329000</v>
       </c>
       <c r="K54" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="L54" s="3">
         <v>1333900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1342000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1346100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1385800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1328800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1292700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1238300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1204700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1172200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1114700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>951400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>958300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>943700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>934100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>893400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>854800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,49 +4184,50 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1200</v>
+        <v>1409700</v>
       </c>
       <c r="E57" s="3">
-        <v>1300</v>
+        <v>1364300</v>
       </c>
       <c r="F57" s="3">
-        <v>700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1000</v>
+        <v>1337800</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H57" s="3">
-        <v>400</v>
+        <v>1180100</v>
       </c>
       <c r="I57" s="3">
-        <v>400</v>
+        <v>1165500</v>
       </c>
       <c r="J57" s="3">
+        <v>1166200</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>200</v>
       </c>
       <c r="Q57" s="3">
         <v>200</v>
@@ -4111,51 +4242,54 @@
         <v>200</v>
       </c>
       <c r="U57" s="3">
+        <v>200</v>
+      </c>
+      <c r="V57" s="3">
         <v>300</v>
-      </c>
-      <c r="V57" s="3">
-        <v>400</v>
       </c>
       <c r="W57" s="3">
         <v>400</v>
       </c>
       <c r="X57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>500</v>
       </c>
       <c r="Z57" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>23400</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>30000</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>38300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4203,36 +4337,39 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>749200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -4280,36 +4417,39 @@
         <v>0</v>
       </c>
       <c r="Z59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1431200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>1388900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
+        <v>1369200</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1226500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1204200</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1224000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -4362,31 +4502,34 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20000</v>
+        <v>25200</v>
       </c>
       <c r="E61" s="3">
-        <v>20000</v>
+        <v>25200</v>
       </c>
       <c r="F61" s="3">
-        <v>20000</v>
+        <v>25200</v>
       </c>
       <c r="G61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>20000</v>
+        <v>25200</v>
       </c>
       <c r="I61" s="3">
-        <v>20000</v>
+        <v>25200</v>
       </c>
       <c r="J61" s="3">
-        <v>20000</v>
+        <v>25900</v>
       </c>
       <c r="K61" s="3">
         <v>20000</v>
@@ -4407,7 +4550,7 @@
         <v>20000</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -4439,31 +4582,34 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>20300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+        <v>15000</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>12200</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>12700</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4516,8 +4662,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,22 +4902,25 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1476600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1427700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1409300</v>
       </c>
-      <c r="F66" s="3">
-        <v>1372500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1296700</v>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H66" s="3">
         <v>1263900</v>
@@ -4774,58 +4932,61 @@
         <v>1249900</v>
       </c>
       <c r="K66" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="L66" s="3">
         <v>1261800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1256800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1245100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1259700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1200700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1163100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1116300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1082100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1055300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1001500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>846500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>852900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>837600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>832200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>795600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>762000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,22 +5332,25 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E72" s="3">
         <v>102900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>100600</v>
       </c>
-      <c r="F72" s="3">
-        <v>98600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>98400</v>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3">
         <v>96600</v>
@@ -5188,58 +5362,61 @@
         <v>91700</v>
       </c>
       <c r="K72" s="3">
+        <v>91700</v>
+      </c>
+      <c r="L72" s="3">
         <v>89100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>83800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>80400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>76800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>75500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>72300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>69000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>64400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>62000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>59200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>57800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>55000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>53700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>68300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,22 +5652,25 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>112800</v>
+      </c>
+      <c r="E76" s="3">
         <v>105400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>102600</v>
       </c>
-      <c r="F76" s="3">
-        <v>98500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>85600</v>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H76" s="3">
         <v>90900</v>
@@ -5496,58 +5682,61 @@
         <v>79100</v>
       </c>
       <c r="K76" s="3">
+        <v>79100</v>
+      </c>
+      <c r="L76" s="3">
         <v>72200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>85200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>101000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>126100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>128000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>129700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>122000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>122700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>116900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>113200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>104900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>105400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>106100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>101900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>97800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>92700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,24 +5812,27 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
-      </c>
-      <c r="F80" s="2">
-        <v>45291</v>
       </c>
       <c r="G80" s="2">
         <v>45199</v>
@@ -5655,69 +5847,72 @@
         <v>44926</v>
       </c>
       <c r="K80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2700</v>
-      </c>
-      <c r="F81" s="3">
-        <v>900</v>
       </c>
       <c r="G81" s="3">
         <v>2500</v>
@@ -5732,58 +5927,61 @@
         <v>3300</v>
       </c>
       <c r="K81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L81" s="3">
         <v>5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,31 +6009,32 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5888,8 +6087,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,31 +6487,34 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3">
         <v>0</v>
@@ -6350,8 +6567,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,31 +6599,32 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6456,8 +6677,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,31 +6837,34 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6687,8 +6917,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,31 +6949,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,31 +7267,34 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -7101,31 +7347,34 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7178,31 +7427,34 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -7253,6 +7505,9 @@
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,205 +656,210 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44926</v>
       </c>
       <c r="K7" s="2">
         <v>44926</v>
       </c>
       <c r="L7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E8" s="3">
         <v>18000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I8" s="3">
         <v>16200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>16100</v>
       </c>
-      <c r="I8" s="3">
-        <v>15400</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>11900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,35 +938,38 @@
       <c r="AB9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E10" s="3">
         <v>18000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>15200</v>
+      </c>
+      <c r="I10" s="3">
         <v>16200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>16100</v>
       </c>
-      <c r="I10" s="3">
-        <v>15400</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>15800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1013,8 +1021,11 @@
       <c r="AB10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1043,8 +1054,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1123,8 +1135,11 @@
       <c r="AB12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,8 +1218,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1229,8 +1247,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1283,8 +1301,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1298,10 +1319,10 @@
         <v>600</v>
       </c>
       <c r="G15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="I15" s="3">
         <v>500</v>
@@ -1309,8 +1330,8 @@
       <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
+      <c r="K15" s="3">
+        <v>500</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
@@ -1321,8 +1342,8 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1363,8 +1384,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,88 +1414,92 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E17" s="3">
         <v>14400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I17" s="3">
         <v>13000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>12400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>11000</v>
       </c>
       <c r="J17" s="3">
         <v>12400</v>
       </c>
       <c r="K17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>11400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1479,79 +1507,82 @@
         <v>3500</v>
       </c>
       <c r="E18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F18" s="3">
         <v>3900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I18" s="3">
         <v>3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>3800</v>
       </c>
-      <c r="I18" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>9200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,115 +1611,119 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>300</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
-      </c>
-      <c r="F20" s="3">
-        <v>200</v>
       </c>
       <c r="G20" s="3">
         <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>200</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>6600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E21" s="3">
         <v>3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I21" s="3">
         <v>3500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>4200</v>
       </c>
-      <c r="I21" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1740,8 +1775,11 @@
       <c r="AB21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1766,8 +1804,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1815,173 +1853,182 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>1700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E23" s="3">
         <v>3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I23" s="3">
         <v>3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>3700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J23" s="3">
-        <v>3400</v>
       </c>
       <c r="K23" s="3">
         <v>3400</v>
       </c>
       <c r="L23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M23" s="3">
         <v>7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>11500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2300</v>
-      </c>
-      <c r="X23" s="3">
-        <v>3800</v>
       </c>
       <c r="Y23" s="3">
         <v>3800</v>
       </c>
       <c r="Z23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA23" s="3">
         <v>3400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
       </c>
       <c r="H24" s="3">
+        <v>300</v>
+      </c>
+      <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>700</v>
-      </c>
-      <c r="I24" s="3">
-        <v>700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>100</v>
       </c>
       <c r="K24" s="3">
         <v>100</v>
       </c>
       <c r="L24" s="3">
+        <v>100</v>
+      </c>
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
-      </c>
-      <c r="S24" s="3">
-        <v>600</v>
       </c>
       <c r="T24" s="3">
         <v>600</v>
       </c>
       <c r="U24" s="3">
+        <v>600</v>
+      </c>
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
-      </c>
-      <c r="X24" s="3">
-        <v>500</v>
       </c>
       <c r="Y24" s="3">
         <v>500</v>
       </c>
       <c r="Z24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2107,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>900</v>
+      </c>
+      <c r="I26" s="3">
         <v>2500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
-      </c>
-      <c r="I26" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J26" s="3">
-        <v>3300</v>
       </c>
       <c r="K26" s="3">
         <v>3300</v>
       </c>
       <c r="L26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M26" s="3">
         <v>5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>900</v>
+      </c>
+      <c r="I27" s="3">
         <v>2500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>3000</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>3300</v>
       </c>
       <c r="K27" s="3">
         <v>3300</v>
       </c>
       <c r="L27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M27" s="3">
         <v>5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>1900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2356,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2439,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2522,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2605,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-200</v>
       </c>
       <c r="G32" s="3">
         <v>-200</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-200</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>7400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>900</v>
+      </c>
+      <c r="I33" s="3">
         <v>2500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>3000</v>
-      </c>
-      <c r="I33" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>3300</v>
       </c>
       <c r="K33" s="3">
         <v>3300</v>
       </c>
       <c r="L33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M33" s="3">
         <v>5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2854,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>900</v>
+      </c>
+      <c r="I35" s="3">
         <v>2500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>3000</v>
-      </c>
-      <c r="I35" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>3300</v>
       </c>
       <c r="K35" s="3">
         <v>3300</v>
       </c>
       <c r="L35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M35" s="3">
         <v>5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44926</v>
       </c>
       <c r="K38" s="2">
         <v>44926</v>
       </c>
       <c r="L38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3058,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,168 +3089,175 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E41" s="3">
         <v>37200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>39200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>29100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H41" s="3">
-        <v>26400</v>
-      </c>
-      <c r="I41" s="3">
-        <v>25200</v>
+        <v>36200</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J41" s="3">
         <v>26400</v>
       </c>
       <c r="K41" s="3">
+        <v>26400</v>
+      </c>
+      <c r="L41" s="3">
         <v>52100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>50600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>54000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>45000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>43400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>50000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>39800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>31200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>47000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>50100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>68500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>49400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>50500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>81400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E42" s="3">
         <v>34800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>9300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>11200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>8900</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>15400</v>
       </c>
-      <c r="I42" s="3">
-        <v>9400</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>8100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4900</v>
-      </c>
-      <c r="M42" s="3">
-        <v>6700</v>
       </c>
       <c r="N42" s="3">
         <v>6700</v>
       </c>
       <c r="O42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P42" s="3">
         <v>7700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>7500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>23300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>28500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>59500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>46100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>16000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>6700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>35700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>35400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>37400</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3191,8 +3282,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3245,8 +3336,11 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3254,26 +3348,26 @@
         <v>700</v>
       </c>
       <c r="E44" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F44" s="3">
         <v>800</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>5</v>
+      <c r="G44" s="3">
+        <v>800</v>
       </c>
       <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
+        <v>800</v>
+      </c>
+      <c r="K44" s="3">
         <v>1000</v>
       </c>
-      <c r="J44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
@@ -3325,35 +3419,38 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E45" s="3">
         <v>36700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>44200</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H45" s="3">
+        <v>34900</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>37400</v>
       </c>
-      <c r="I45" s="3">
-        <v>40200</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33100</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -3405,35 +3502,38 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>66400</v>
+      </c>
+      <c r="E46" s="3">
         <v>110000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>88500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>85400</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H46" s="3">
+        <v>80900</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3">
         <v>80600</v>
       </c>
-      <c r="I46" s="3">
-        <v>75800</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>68600</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -3485,35 +3585,38 @@
       <c r="AB46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>502100</v>
+      </c>
+      <c r="E47" s="3">
         <v>521400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>495300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>500700</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H47" s="3">
+        <v>486700</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>421000</v>
       </c>
-      <c r="I47" s="3">
-        <v>434900</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>449700</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -3560,93 +3663,99 @@
         <v>0</v>
       </c>
       <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
         <v>730900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E48" s="3">
         <v>21100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H48" s="3">
+        <v>22000</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>22700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>23200</v>
-      </c>
-      <c r="J48" s="3">
-        <v>23900</v>
       </c>
       <c r="K48" s="3">
         <v>23900</v>
       </c>
       <c r="L48" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="M48" s="3">
         <v>23700</v>
       </c>
       <c r="N48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="O48" s="3">
         <v>22900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>20800</v>
-      </c>
-      <c r="T48" s="3">
-        <v>20600</v>
       </c>
       <c r="U48" s="3">
         <v>20600</v>
       </c>
       <c r="V48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="W48" s="3">
         <v>18500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>17600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>16700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3660,10 +3769,10 @@
         <v>5300</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
@@ -3671,8 +3780,8 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>5</v>
@@ -3683,8 +3792,8 @@
       <c r="N49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3725,8 +3834,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3917,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,35 +4000,38 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E52" s="3">
         <v>68500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H52" s="3">
+        <v>46100</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>62400</v>
       </c>
-      <c r="I52" s="3">
-        <v>52600</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38400</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -3965,8 +4083,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4166,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1524600</v>
+      </c>
+      <c r="E54" s="3">
         <v>1589300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1533100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1511900</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H54" s="3">
+        <v>1466500</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>1354800</v>
-      </c>
-      <c r="I54" s="3">
-        <v>1331400</v>
-      </c>
-      <c r="J54" s="3">
-        <v>1329000</v>
       </c>
       <c r="K54" s="3">
         <v>1329000</v>
       </c>
       <c r="L54" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="M54" s="3">
         <v>1333900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1342000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1346100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1385800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1328800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1292700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1238300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1204700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1172200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1114700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>951400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>958300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>943700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>934100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>893400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>854800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4282,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,52 +4313,53 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1371400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1409700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1364300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1337800</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H57" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>1180100</v>
       </c>
-      <c r="I57" s="3">
-        <v>1165500</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1166200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>200</v>
       </c>
       <c r="R57" s="3">
         <v>200</v>
@@ -4245,55 +4374,58 @@
         <v>200</v>
       </c>
       <c r="V57" s="3">
+        <v>200</v>
+      </c>
+      <c r="W57" s="3">
         <v>300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
       </c>
       <c r="Y57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>500</v>
       </c>
       <c r="AA57" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
         <v>20000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>23400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>30000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>66400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>46000</v>
       </c>
-      <c r="I58" s="3">
-        <v>38300</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>46100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4340,13 +4472,16 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>749200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4371,8 +4506,8 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
+      <c r="K59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L59" s="3">
         <v>0</v>
@@ -4420,40 +4555,43 @@
         <v>0</v>
       </c>
       <c r="AA59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1386600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1431200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1388900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1369200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H60" s="3">
+        <v>1339000</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3">
         <v>1226500</v>
       </c>
-      <c r="I60" s="3">
-        <v>1204200</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1224000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -4505,13 +4643,16 @@
       <c r="AB60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>25200</v>
+        <v>25700</v>
       </c>
       <c r="E61" s="3">
         <v>25200</v>
@@ -4520,19 +4661,19 @@
         <v>25200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>25200</v>
       </c>
       <c r="H61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>25200</v>
       </c>
-      <c r="I61" s="3">
-        <v>25200</v>
-      </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>25900</v>
-      </c>
-      <c r="K61" s="3">
-        <v>20000</v>
       </c>
       <c r="L61" s="3">
         <v>20000</v>
@@ -4553,7 +4694,7 @@
         <v>20000</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4585,34 +4726,37 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>20300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15000</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>12200</v>
       </c>
-      <c r="I62" s="3">
-        <v>12700</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4665,8 +4809,11 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4892,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4975,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5058,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1412900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1476600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1427700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1409300</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H66" s="3">
+        <v>1368000</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>1263900</v>
-      </c>
-      <c r="I66" s="3">
-        <v>1242100</v>
-      </c>
-      <c r="J66" s="3">
-        <v>1249900</v>
       </c>
       <c r="K66" s="3">
         <v>1249900</v>
       </c>
       <c r="L66" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="M66" s="3">
         <v>1261800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1256800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1245100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1259700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1200700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1163100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1116300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1082100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1055300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1001500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>846500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>852900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>837600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>832200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>795600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>762000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5174,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5255,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5338,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5421,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5504,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E72" s="3">
         <v>104800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>102900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>100600</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H72" s="3">
+        <v>98600</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>96600</v>
-      </c>
-      <c r="I72" s="3">
-        <v>94300</v>
-      </c>
-      <c r="J72" s="3">
-        <v>91700</v>
       </c>
       <c r="K72" s="3">
         <v>91700</v>
       </c>
       <c r="L72" s="3">
+        <v>91700</v>
+      </c>
+      <c r="M72" s="3">
         <v>89100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>83800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>80400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>75500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>72300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>69000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>64400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>62000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>59200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>57800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>55000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>53700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>68300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5670,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5753,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5836,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E76" s="3">
         <v>112800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>105400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>102600</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H76" s="3">
+        <v>98500</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>90900</v>
-      </c>
-      <c r="I76" s="3">
-        <v>89300</v>
-      </c>
-      <c r="J76" s="3">
-        <v>79100</v>
       </c>
       <c r="K76" s="3">
         <v>79100</v>
       </c>
       <c r="L76" s="3">
+        <v>79100</v>
+      </c>
+      <c r="M76" s="3">
         <v>72200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>85200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>101000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>126100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>128000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>129700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>122000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>122700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>116900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>113200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>104900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>105400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>106100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>101900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>97800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>92700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6002,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44926</v>
       </c>
       <c r="K80" s="2">
         <v>44926</v>
       </c>
       <c r="L80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>900</v>
+      </c>
+      <c r="I81" s="3">
         <v>2500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>3000</v>
-      </c>
-      <c r="I81" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>3300</v>
       </c>
       <c r="K81" s="3">
         <v>3300</v>
       </c>
       <c r="L81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M81" s="3">
         <v>5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6206,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6036,8 +6233,8 @@
       <c r="J83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -6090,8 +6287,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6370,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6453,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6536,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6619,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6702,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6516,8 +6731,8 @@
       <c r="J89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -6570,8 +6785,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,8 +6818,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6626,8 +6845,8 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6680,8 +6899,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6982,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7065,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6866,8 +7094,8 @@
       <c r="J94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -6920,8 +7148,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7181,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7208,8 @@
       <c r="J96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7030,8 +7262,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7345,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7428,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7511,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7296,8 +7540,8 @@
       <c r="J100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -7350,8 +7594,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7376,8 +7623,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7430,8 +7677,11 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7456,8 +7706,8 @@
       <c r="J102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -7508,6 +7758,9 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,210 +656,217 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
-      </c>
-      <c r="K7" s="2">
-        <v>44926</v>
       </c>
       <c r="L7" s="2">
         <v>44926</v>
       </c>
       <c r="M7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E8" s="3">
         <v>17500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>11900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>11200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>11700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>8900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -941,38 +948,41 @@
       <c r="AC9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E10" s="3">
         <v>17500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>18000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>17000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>15600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>16200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>15800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1024,8 +1034,11 @@
       <c r="AC10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1068,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1138,8 +1152,11 @@
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1221,8 +1238,11 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1250,8 +1270,8 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1304,8 +1324,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1325,7 +1348,7 @@
         <v>600</v>
       </c>
       <c r="I15" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J15" s="3">
         <v>500</v>
@@ -1333,8 +1356,8 @@
       <c r="K15" s="3">
         <v>500</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
+      <c r="L15" s="3">
+        <v>500</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>5</v>
@@ -1345,8 +1368,8 @@
       <c r="O15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1387,8 +1410,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1415,174 +1441,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>13900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13000</v>
-      </c>
-      <c r="J17" s="3">
-        <v>12400</v>
       </c>
       <c r="K17" s="3">
         <v>12400</v>
       </c>
       <c r="L17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>11400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3500</v>
+        <v>-5500</v>
       </c>
       <c r="E18" s="3">
         <v>3500</v>
       </c>
       <c r="F18" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G18" s="3">
         <v>3900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1612,22 +1645,23 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>200</v>
       </c>
       <c r="H20" s="3">
         <v>200</v>
@@ -1636,97 +1670,100 @@
         <v>200</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-7400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3900</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1778,8 +1815,11 @@
       <c r="AC21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1807,8 +1847,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1856,179 +1896,188 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>1700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>3400</v>
       </c>
       <c r="L23" s="3">
         <v>3400</v>
       </c>
       <c r="M23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N23" s="3">
         <v>7200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2300</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>3800</v>
       </c>
       <c r="Z23" s="3">
         <v>3800</v>
       </c>
       <c r="AA23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB23" s="3">
         <v>3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
-      </c>
-      <c r="K24" s="3">
-        <v>100</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
+        <v>100</v>
+      </c>
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
-      </c>
-      <c r="T24" s="3">
-        <v>600</v>
       </c>
       <c r="U24" s="3">
         <v>600</v>
       </c>
       <c r="V24" s="3">
+        <v>600</v>
+      </c>
+      <c r="W24" s="3">
         <v>300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>400</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>500</v>
       </c>
       <c r="Z24" s="3">
         <v>500</v>
       </c>
       <c r="AA24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB24" s="3">
         <v>400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2110,174 +2159,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E26" s="3">
         <v>3000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3000</v>
-      </c>
-      <c r="K26" s="3">
-        <v>3300</v>
       </c>
       <c r="L26" s="3">
         <v>3300</v>
       </c>
       <c r="M26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N26" s="3">
         <v>5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>5300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>3000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3000</v>
-      </c>
-      <c r="K27" s="3">
-        <v>3300</v>
       </c>
       <c r="L27" s="3">
         <v>3300</v>
       </c>
       <c r="M27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N27" s="3">
         <v>5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>5300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>1900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2359,8 +2417,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2442,8 +2503,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2525,8 +2589,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2608,22 +2675,25 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-200</v>
       </c>
       <c r="H32" s="3">
         <v>-200</v>
@@ -2632,150 +2702,156 @@
         <v>-200</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>7400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>3000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3000</v>
-      </c>
-      <c r="K33" s="3">
-        <v>3300</v>
       </c>
       <c r="L33" s="3">
         <v>3300</v>
       </c>
       <c r="M33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N33" s="3">
         <v>5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>5300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>1900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2857,179 +2933,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>3000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3000</v>
-      </c>
-      <c r="K35" s="3">
-        <v>3300</v>
       </c>
       <c r="L35" s="3">
         <v>3300</v>
       </c>
       <c r="M35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N35" s="3">
         <v>5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>5300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>1900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
-      </c>
-      <c r="K38" s="2">
-        <v>44926</v>
       </c>
       <c r="L38" s="2">
         <v>44926</v>
       </c>
       <c r="M38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3059,8 +3144,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3090,174 +3176,181 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E41" s="3">
         <v>31300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>37200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36200</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" s="3">
-        <v>26400</v>
+      <c r="J41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K41" s="3">
         <v>26400</v>
       </c>
       <c r="L41" s="3">
+        <v>26400</v>
+      </c>
+      <c r="M41" s="3">
         <v>52100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>50600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>58600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>54000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>45000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>43400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>50000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>47000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>50100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>42400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>68500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>49400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>50500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>81400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E42" s="3">
         <v>5600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>34800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>11200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>8900</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>15400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4900</v>
-      </c>
-      <c r="N42" s="3">
-        <v>6700</v>
       </c>
       <c r="O42" s="3">
         <v>6700</v>
       </c>
       <c r="P42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q42" s="3">
         <v>7700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>7500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>23300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>28500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>59500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>46100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>16000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>6700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>35700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>2000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>35400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>37400</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
-      </c>
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3285,8 +3378,8 @@
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3339,8 +3432,11 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3351,7 +3447,7 @@
         <v>700</v>
       </c>
       <c r="F44" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="G44" s="3">
         <v>800</v>
@@ -3359,18 +3455,18 @@
       <c r="H44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="I44" s="3">
         <v>800</v>
       </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="K44" s="3">
+        <v>800</v>
+      </c>
+      <c r="L44" s="3">
         <v>1000</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
@@ -3422,8 +3518,11 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3431,29 +3530,29 @@
         <v>28800</v>
       </c>
       <c r="E45" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F45" s="3">
         <v>36700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>44200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3">
         <v>37400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33100</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3505,38 +3604,41 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E46" s="3">
         <v>66400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>110000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>88500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>85400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>80900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K46" s="3">
         <v>80600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>68600</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3588,38 +3690,41 @@
       <c r="AC46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>549300</v>
+      </c>
+      <c r="E47" s="3">
         <v>502100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>521400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>495300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>500700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>486700</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
         <v>421000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>449700</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3666,96 +3771,102 @@
         <v>0</v>
       </c>
       <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3">
         <v>730900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E48" s="3">
         <v>20800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>21100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>22000</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>22700</v>
-      </c>
-      <c r="K48" s="3">
-        <v>23900</v>
       </c>
       <c r="L48" s="3">
         <v>23900</v>
       </c>
       <c r="M48" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="N48" s="3">
         <v>23700</v>
       </c>
       <c r="O48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="P48" s="3">
         <v>22900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>22800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>20800</v>
-      </c>
-      <c r="U48" s="3">
-        <v>20600</v>
       </c>
       <c r="V48" s="3">
         <v>20600</v>
       </c>
       <c r="W48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="X48" s="3">
         <v>18500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>18300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>17600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>16700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3775,7 +3886,7 @@
         <v>5300</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -3783,8 +3894,8 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
@@ -3795,8 +3906,8 @@
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3837,8 +3948,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3920,8 +4034,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4003,38 +4120,41 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E52" s="3">
         <v>48700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>68500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>46100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="3">
         <v>62400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38400</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
         <v>0</v>
       </c>
@@ -4086,8 +4206,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4169,91 +4292,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1607200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1524600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1589300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1533100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1511900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1466500</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="3">
         <v>1354800</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1329000</v>
       </c>
       <c r="L54" s="3">
         <v>1329000</v>
       </c>
       <c r="M54" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="N54" s="3">
         <v>1333900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1342000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1346100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1385800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1328800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1292700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1238300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1204700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1172200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1114700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>951400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>958300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>943700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>934100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>893400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>854800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4283,8 +4412,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4314,55 +4444,56 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1429600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1371400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1409700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1364300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1337800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1266000</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K57" s="3">
         <v>1180100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1166200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>300</v>
-      </c>
-      <c r="R57" s="3">
-        <v>200</v>
       </c>
       <c r="S57" s="3">
         <v>200</v>
@@ -4377,58 +4508,61 @@
         <v>200</v>
       </c>
       <c r="W57" s="3">
+        <v>200</v>
+      </c>
+      <c r="X57" s="3">
         <v>300</v>
-      </c>
-      <c r="X57" s="3">
-        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
       </c>
       <c r="Z57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AA57" s="3">
         <v>500</v>
       </c>
       <c r="AB57" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>6500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>23400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>30000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>66400</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>46000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46100</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4475,13 +4609,16 @@
         <v>0</v>
       </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>749200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4509,8 +4646,8 @@
       <c r="K59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
+      <c r="L59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -4558,43 +4695,46 @@
         <v>0</v>
       </c>
       <c r="AB59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1431100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1386600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1431200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1388900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1369200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1339000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="3">
         <v>1226500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1224000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -4646,16 +4786,19 @@
       <c r="AC60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>50200</v>
+      </c>
+      <c r="E61" s="3">
         <v>25700</v>
-      </c>
-      <c r="E61" s="3">
-        <v>25200</v>
       </c>
       <c r="F61" s="3">
         <v>25200</v>
@@ -4664,19 +4807,19 @@
         <v>25200</v>
       </c>
       <c r="H61" s="3">
+        <v>25200</v>
+      </c>
+      <c r="I61" s="3">
         <v>25900</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>25200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>25900</v>
-      </c>
-      <c r="L61" s="3">
-        <v>20000</v>
       </c>
       <c r="M61" s="3">
         <v>20000</v>
@@ -4697,7 +4840,7 @@
         <v>20000</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4729,37 +4872,40 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>15000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>12200</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4812,8 +4958,11 @@
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4895,8 +5044,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4978,8 +5130,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5061,91 +5216,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1492500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1412900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1476600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1427700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1409300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1368000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K66" s="3">
         <v>1263900</v>
-      </c>
-      <c r="K66" s="3">
-        <v>1249900</v>
       </c>
       <c r="L66" s="3">
         <v>1249900</v>
       </c>
       <c r="M66" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="N66" s="3">
         <v>1261800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1256800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1245100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1259700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1200700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1163100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1116300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1082100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1055300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1001500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>846500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>852900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>837600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>832200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>795600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>762000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5175,8 +5336,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5258,8 +5420,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5341,8 +5506,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5424,8 +5592,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5507,91 +5678,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E72" s="3">
         <v>107100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>104800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>102900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>100600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>98600</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K72" s="3">
         <v>96600</v>
-      </c>
-      <c r="K72" s="3">
-        <v>91700</v>
       </c>
       <c r="L72" s="3">
         <v>91700</v>
       </c>
       <c r="M72" s="3">
+        <v>91700</v>
+      </c>
+      <c r="N72" s="3">
         <v>89100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>83800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>80400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>76800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>75500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>72300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>69000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>64400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>62000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>59200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>57800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>55000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>53700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>68300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5673,8 +5850,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5756,8 +5936,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5839,91 +6022,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E76" s="3">
         <v>111700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>112800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>105400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>102600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>98500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K76" s="3">
         <v>90900</v>
-      </c>
-      <c r="K76" s="3">
-        <v>79100</v>
       </c>
       <c r="L76" s="3">
         <v>79100</v>
       </c>
       <c r="M76" s="3">
+        <v>79100</v>
+      </c>
+      <c r="N76" s="3">
         <v>72200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>85200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>126100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>128000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>129700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>122000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>122700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>116900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>113200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>104900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>105400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>106100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>101900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>97800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>92700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6005,179 +6194,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
-      </c>
-      <c r="K80" s="2">
-        <v>44926</v>
       </c>
       <c r="L80" s="2">
         <v>44926</v>
       </c>
       <c r="M80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>3000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3000</v>
-      </c>
-      <c r="K81" s="3">
-        <v>3300</v>
       </c>
       <c r="L81" s="3">
         <v>3300</v>
       </c>
       <c r="M81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N81" s="3">
         <v>5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>5300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>1900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6207,8 +6405,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6236,8 +6435,8 @@
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6290,8 +6489,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6373,8 +6575,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6456,8 +6661,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6539,8 +6747,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6622,8 +6833,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6705,8 +6919,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6734,8 +6951,8 @@
       <c r="K89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L89" s="3">
-        <v>0</v>
+      <c r="L89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M89" s="3">
         <v>0</v>
@@ -6788,8 +7005,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6819,8 +7039,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6848,8 +7069,8 @@
       <c r="K91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -6902,8 +7123,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6985,8 +7209,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7068,8 +7295,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7097,8 +7327,8 @@
       <c r="K94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -7151,8 +7381,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7182,8 +7415,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,8 +7445,8 @@
       <c r="K96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7265,8 +7499,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7348,8 +7585,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7431,8 +7671,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7514,8 +7757,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7543,8 +7789,8 @@
       <c r="K100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -7597,8 +7843,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,8 +7875,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7680,8 +7929,11 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7709,8 +7961,8 @@
       <c r="K102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="L102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -7761,6 +8013,9 @@
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CPKF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="92">
   <si>
     <t>CPKF</t>
   </si>
@@ -656,217 +656,224 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
-      </c>
-      <c r="L7" s="2">
-        <v>44926</v>
       </c>
       <c r="M7" s="2">
         <v>44926</v>
       </c>
       <c r="N7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
         <v>17500</v>
       </c>
-      <c r="F8" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H8" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3">
         <v>15200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>11900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>11200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>11100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>22300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>11700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>9600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>8400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>8600</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -951,41 +958,44 @@
       <c r="AD9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>8300</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
         <v>17500</v>
       </c>
-      <c r="F10" s="3">
-        <v>18000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>17000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>15600</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
         <v>15200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>16200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>16100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>15800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1037,8 +1047,11 @@
       <c r="AD10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1069,8 +1082,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1155,8 +1169,11 @@
       <c r="AD12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1241,8 +1258,11 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1273,8 +1293,8 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1327,31 +1347,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>600</v>
       </c>
       <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>600</v>
-      </c>
-      <c r="J15" s="3">
-        <v>500</v>
       </c>
       <c r="K15" s="3">
         <v>500</v>
@@ -1359,8 +1382,8 @@
       <c r="L15" s="3">
         <v>500</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
+      <c r="M15" s="3">
+        <v>500</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>5</v>
@@ -1371,8 +1394,8 @@
       <c r="P15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1413,8 +1436,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1442,180 +1468,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>13900</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
         <v>13800</v>
       </c>
-      <c r="E17" s="3">
-        <v>13900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>14400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>13100</v>
-      </c>
-      <c r="H17" s="3">
-        <v>12100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>13800</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13000</v>
-      </c>
-      <c r="K17" s="3">
-        <v>12400</v>
       </c>
       <c r="L17" s="3">
         <v>12400</v>
       </c>
       <c r="M17" s="3">
+        <v>12400</v>
+      </c>
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>11400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5800</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="E18" s="3">
-        <v>3500</v>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F18" s="3">
         <v>3500</v>
       </c>
-      <c r="G18" s="3">
-        <v>3900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
         <v>1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1646,127 +1679,131 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>200</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
-        <v>400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
-        <v>200</v>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J20" s="3">
         <v>200</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-8000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-7400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-5200</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>3900</v>
       </c>
-      <c r="F21" s="3">
-        <v>3700</v>
-      </c>
       <c r="G21" s="3">
-        <v>4300</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>3500</v>
+      </c>
+      <c r="L21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="M21" s="3">
         <v>3900</v>
       </c>
-      <c r="I21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="J21" s="3">
-        <v>3500</v>
-      </c>
-      <c r="K21" s="3">
-        <v>4200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>3900</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1818,8 +1855,11 @@
       <c r="AD21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1850,8 +1890,8 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1899,185 +1939,194 @@
         <v>0</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>1700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-5800</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
         <v>3300</v>
       </c>
-      <c r="F23" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L23" s="3">
         <v>3700</v>
-      </c>
-      <c r="H23" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I23" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>3000</v>
-      </c>
-      <c r="K23" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L23" s="3">
-        <v>3400</v>
       </c>
       <c r="M23" s="3">
         <v>3400</v>
       </c>
       <c r="N23" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>2300</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>3800</v>
       </c>
       <c r="AA23" s="3">
         <v>3800</v>
       </c>
       <c r="AB23" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AC23" s="3">
         <v>3400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>300</v>
+      </c>
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>700</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
       <c r="N24" s="3">
+        <v>100</v>
+      </c>
+      <c r="O24" s="3">
         <v>1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
-      </c>
-      <c r="U24" s="3">
-        <v>600</v>
       </c>
       <c r="V24" s="3">
         <v>600</v>
       </c>
       <c r="W24" s="3">
+        <v>600</v>
+      </c>
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>500</v>
       </c>
       <c r="AA24" s="3">
         <v>500</v>
       </c>
       <c r="AB24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2162,180 +2211,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
         <v>3000</v>
       </c>
-      <c r="F26" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>900</v>
+      </c>
+      <c r="K26" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L26" s="3">
         <v>3000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>900</v>
-      </c>
-      <c r="J26" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L26" s="3">
-        <v>3300</v>
       </c>
       <c r="M26" s="3">
         <v>3300</v>
       </c>
       <c r="N26" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O26" s="3">
         <v>5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
         <v>3000</v>
       </c>
-      <c r="F27" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>900</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L27" s="3">
         <v>3000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I27" s="3">
-        <v>900</v>
-      </c>
-      <c r="J27" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L27" s="3">
-        <v>3300</v>
       </c>
       <c r="M27" s="3">
         <v>3300</v>
       </c>
       <c r="N27" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O27" s="3">
         <v>5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2420,8 +2478,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2506,8 +2567,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2592,8 +2656,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2678,180 +2745,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-200</v>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J32" s="3">
         <v>-200</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>8000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>7400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
         <v>3000</v>
       </c>
-      <c r="F33" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>900</v>
+      </c>
+      <c r="K33" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L33" s="3">
         <v>3000</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I33" s="3">
-        <v>900</v>
-      </c>
-      <c r="J33" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L33" s="3">
-        <v>3300</v>
       </c>
       <c r="M33" s="3">
         <v>3300</v>
       </c>
       <c r="N33" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O33" s="3">
         <v>5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2936,185 +3012,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
         <v>3000</v>
       </c>
-      <c r="F35" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>900</v>
+      </c>
+      <c r="K35" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L35" s="3">
         <v>3000</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I35" s="3">
-        <v>900</v>
-      </c>
-      <c r="J35" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L35" s="3">
-        <v>3300</v>
       </c>
       <c r="M35" s="3">
         <v>3300</v>
       </c>
       <c r="N35" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O35" s="3">
         <v>5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
-      </c>
-      <c r="L38" s="2">
-        <v>44926</v>
       </c>
       <c r="M38" s="2">
         <v>44926</v>
       </c>
       <c r="N38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3145,8 +3230,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3177,180 +3263,187 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>31400</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="3">
         <v>31300</v>
       </c>
-      <c r="F41" s="3">
-        <v>37200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>39200</v>
-      </c>
-      <c r="H41" s="3">
-        <v>29100</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J41" s="3">
         <v>36200</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K41" s="3">
-        <v>26400</v>
+      <c r="K41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L41" s="3">
         <v>26400</v>
       </c>
       <c r="M41" s="3">
+        <v>26400</v>
+      </c>
+      <c r="N41" s="3">
         <v>52100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>50600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>58600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>43400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>50000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>31200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>47000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>50100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>42400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>68500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>49400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>50500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>81400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>20100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5600</v>
       </c>
-      <c r="F42" s="3">
-        <v>34800</v>
-      </c>
       <c r="G42" s="3">
-        <v>9300</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>8900</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>15400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4900</v>
-      </c>
-      <c r="O42" s="3">
-        <v>6700</v>
       </c>
       <c r="P42" s="3">
         <v>6700</v>
       </c>
       <c r="Q42" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R42" s="3">
         <v>7700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>7500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>23300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>28500</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>59500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>46100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>16000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>6700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>35700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>35400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>37400</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3381,8 +3474,8 @@
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3435,41 +3528,44 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>700</v>
-      </c>
-      <c r="E44" s="3">
-        <v>700</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F44" s="3">
         <v>700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3">
         <v>800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3">
         <v>800</v>
       </c>
-      <c r="I44" s="3">
-        <v>800</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K44" s="3">
-        <v>800</v>
-      </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1000</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
       <c r="N44" s="3">
         <v>0</v>
       </c>
@@ -3521,41 +3617,44 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>28800</v>
       </c>
-      <c r="E45" s="3">
-        <v>28800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>36700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>38900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>44200</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>34900</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>37400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33100</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
       <c r="N45" s="3">
         <v>0</v>
       </c>
@@ -3607,41 +3706,44 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>81000</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
         <v>66400</v>
       </c>
-      <c r="F46" s="3">
-        <v>110000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>88500</v>
-      </c>
-      <c r="H46" s="3">
-        <v>85400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J46" s="3">
         <v>80900</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
         <v>80600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>68600</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3693,41 +3795,44 @@
       <c r="AD46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>549300</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>502100</v>
       </c>
-      <c r="F47" s="3">
-        <v>521400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>495300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>500700</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>486700</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>421000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>449700</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -3774,131 +3879,137 @@
         <v>0</v>
       </c>
       <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
         <v>730900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>715800</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>20400</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>20800</v>
       </c>
-      <c r="F48" s="3">
-        <v>21100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>21200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>21600</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>22000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="K48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
         <v>22700</v>
-      </c>
-      <c r="L48" s="3">
-        <v>23900</v>
       </c>
       <c r="M48" s="3">
         <v>23900</v>
       </c>
       <c r="N48" s="3">
-        <v>23700</v>
+        <v>23900</v>
       </c>
       <c r="O48" s="3">
         <v>23700</v>
       </c>
       <c r="P48" s="3">
+        <v>23700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>22900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>20800</v>
-      </c>
-      <c r="V48" s="3">
-        <v>20600</v>
       </c>
       <c r="W48" s="3">
         <v>20600</v>
       </c>
       <c r="X48" s="3">
+        <v>20600</v>
+      </c>
+      <c r="Y48" s="3">
         <v>18500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>18200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>18100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>17600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>16700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>5300</v>
-      </c>
-      <c r="E49" s="3">
-        <v>5300</v>
+      <c r="D49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F49" s="3">
         <v>5300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="3">
         <v>5300</v>
       </c>
-      <c r="H49" s="3">
-        <v>5300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>5300</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>5</v>
@@ -3909,8 +4020,8 @@
       <c r="P49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3951,8 +4062,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4037,8 +4151,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4123,41 +4240,44 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>64400</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
         <v>48700</v>
       </c>
-      <c r="F52" s="3">
-        <v>68500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>55900</v>
-      </c>
-      <c r="H52" s="3">
-        <v>55100</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="3">
         <v>46100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
         <v>62400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38400</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
@@ -4209,8 +4329,11 @@
       <c r="AD52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4295,94 +4418,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>1607200</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F54" s="3">
         <v>1524600</v>
       </c>
-      <c r="F54" s="3">
-        <v>1589300</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1533100</v>
-      </c>
-      <c r="H54" s="3">
-        <v>1511900</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="3">
         <v>1466500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L54" s="3">
         <v>1354800</v>
-      </c>
-      <c r="L54" s="3">
-        <v>1329000</v>
       </c>
       <c r="M54" s="3">
         <v>1329000</v>
       </c>
       <c r="N54" s="3">
+        <v>1329000</v>
+      </c>
+      <c r="O54" s="3">
         <v>1333900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1342000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1346100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1385800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1328800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1292700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1238300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1204700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1172200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1114700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>951400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>958300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>943700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>934100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>893400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>854800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>823200</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4413,8 +4542,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4445,58 +4575,59 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>1429600</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3">
         <v>1371400</v>
       </c>
-      <c r="F57" s="3">
-        <v>1409700</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1364300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1337800</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
         <v>1266000</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
         <v>1180100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1166200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
-      </c>
-      <c r="S57" s="3">
-        <v>200</v>
       </c>
       <c r="T57" s="3">
         <v>200</v>
@@ -4511,61 +4642,64 @@
         <v>200</v>
       </c>
       <c r="X57" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y57" s="3">
         <v>300</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>400</v>
       </c>
       <c r="Z57" s="3">
         <v>400</v>
       </c>
       <c r="AA57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="AB57" s="3">
         <v>500</v>
       </c>
       <c r="AC57" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3">
         <v>6500</v>
       </c>
-      <c r="F58" s="3">
-        <v>20000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>23400</v>
-      </c>
-      <c r="H58" s="3">
-        <v>30000</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3">
         <v>66400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>46000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4612,13 +4746,16 @@
         <v>0</v>
       </c>
       <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>749200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>720500</v>
       </c>
     </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4649,8 +4786,8 @@
       <c r="L59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M59" s="3">
-        <v>0</v>
+      <c r="M59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N59" s="3">
         <v>0</v>
@@ -4698,46 +4835,49 @@
         <v>0</v>
       </c>
       <c r="AC59" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>1431100</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3">
         <v>1386600</v>
       </c>
-      <c r="F60" s="3">
-        <v>1431200</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1388900</v>
-      </c>
-      <c r="H60" s="3">
-        <v>1369200</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3">
         <v>1339000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L60" s="3">
         <v>1226500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1224000</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4789,40 +4929,43 @@
       <c r="AD60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>50200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>25700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>25900</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>25200</v>
       </c>
-      <c r="G61" s="3">
-        <v>25200</v>
-      </c>
-      <c r="H61" s="3">
-        <v>25200</v>
-      </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>25900</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>25200</v>
-      </c>
-      <c r="L61" s="3">
-        <v>25900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>20000</v>
       </c>
       <c r="N61" s="3">
         <v>20000</v>
@@ -4843,7 +4986,7 @@
         <v>20000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4875,40 +5018,43 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>11300</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="F62" s="3">
-        <v>20300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>15000</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>12200</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4961,8 +5107,11 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5047,8 +5196,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5133,8 +5285,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5219,94 +5374,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>1492500</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="3">
         <v>1412900</v>
       </c>
-      <c r="F66" s="3">
-        <v>1476600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1427700</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1409300</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
         <v>1368000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
         <v>1263900</v>
-      </c>
-      <c r="L66" s="3">
-        <v>1249900</v>
       </c>
       <c r="M66" s="3">
         <v>1249900</v>
       </c>
       <c r="N66" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="O66" s="3">
         <v>1261800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1256800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1245100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1259700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1200700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1163100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1116300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1082100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1055300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1001500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>846500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>852900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>837600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>832200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>795600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>762000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>733300</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5337,8 +5498,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5423,8 +5585,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5509,8 +5674,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5595,8 +5763,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5681,94 +5852,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>101900</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" s="3">
         <v>107100</v>
       </c>
-      <c r="F72" s="3">
-        <v>104800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>102900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>100600</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J72" s="3">
         <v>98600</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L72" s="3">
         <v>96600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>91700</v>
       </c>
       <c r="M72" s="3">
         <v>91700</v>
       </c>
       <c r="N72" s="3">
+        <v>91700</v>
+      </c>
+      <c r="O72" s="3">
         <v>89100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>83800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>80400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>76800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>75500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>72300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>69000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>64400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>62000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>59200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>57800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>55000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>53700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>68300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5853,8 +6030,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5939,8 +6119,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6025,94 +6208,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>114600</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F76" s="3">
         <v>111700</v>
       </c>
-      <c r="F76" s="3">
-        <v>112800</v>
-      </c>
-      <c r="G76" s="3">
-        <v>105400</v>
-      </c>
-      <c r="H76" s="3">
-        <v>102600</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J76" s="3">
         <v>98500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L76" s="3">
         <v>90900</v>
-      </c>
-      <c r="L76" s="3">
-        <v>79100</v>
       </c>
       <c r="M76" s="3">
         <v>79100</v>
       </c>
       <c r="N76" s="3">
+        <v>79100</v>
+      </c>
+      <c r="O76" s="3">
         <v>72200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>85200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>101000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>126100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>128000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>129700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>122000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>122700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>116900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>113200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>104900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>105400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>106100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>101900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>97800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>92700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>89900</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6197,185 +6386,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
-      </c>
-      <c r="L80" s="2">
-        <v>44926</v>
       </c>
       <c r="M80" s="2">
         <v>44926</v>
       </c>
       <c r="N80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-4500</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
         <v>3000</v>
       </c>
-      <c r="F81" s="3">
-        <v>2600</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>900</v>
+      </c>
+      <c r="K81" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L81" s="3">
         <v>3000</v>
-      </c>
-      <c r="H81" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I81" s="3">
-        <v>900</v>
-      </c>
-      <c r="J81" s="3">
-        <v>2500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>3000</v>
-      </c>
-      <c r="L81" s="3">
-        <v>3300</v>
       </c>
       <c r="M81" s="3">
         <v>3300</v>
       </c>
       <c r="N81" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O81" s="3">
         <v>5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6406,8 +6604,9 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6438,8 +6637,8 @@
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -6492,8 +6691,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6578,8 +6780,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6664,8 +6869,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6750,8 +6958,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6836,8 +7047,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6922,8 +7136,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6954,8 +7171,8 @@
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N89" s="3">
         <v>0</v>
@@ -7008,8 +7225,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7040,8 +7260,9 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7072,8 +7293,8 @@
       <c r="L91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7126,8 +7347,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7212,8 +7436,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7298,8 +7525,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7330,8 +7560,8 @@
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -7384,8 +7614,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7416,8 +7649,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7448,8 +7682,8 @@
       <c r="L96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7502,8 +7736,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7588,8 +7825,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7674,8 +7914,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7760,8 +8003,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7792,8 +8038,8 @@
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -7846,8 +8092,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7878,8 +8127,8 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7932,8 +8181,11 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7964,8 +8216,8 @@
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -8016,6 +8268,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>
